--- a/codespace/DetroitRiverCase/results/ch4_fw2_stratified_residual_summary.xlsx
+++ b/codespace/DetroitRiverCase/results/ch4_fw2_stratified_residual_summary.xlsx
@@ -475,13 +475,13 @@
         <v>1770</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02719843911007558</v>
+        <v>0.02051662151568967</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04105121611212156</v>
+        <v>0.03154210439067143</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3198601725745047</v>
+        <v>0.2430397747703675</v>
       </c>
     </row>
     <row r="3">
@@ -499,13 +499,13 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02590518118013747</v>
+        <v>0.01479857297528231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02880534584890993</v>
+        <v>0.01769509283640598</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1766503540276511</v>
+        <v>0.08687999726652407</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.615815689051894e-05</v>
+        <v>0.02940591235929491</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.615815689051894e-05</v>
+        <v>0.02940591235929491</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         <v>6105</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02518526300143098</v>
+        <v>0.01683517975696449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03564974164442308</v>
+        <v>0.02386533398223072</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4705040359004168</v>
+        <v>0.3083691373977286</v>
       </c>
     </row>
     <row r="6">
@@ -571,13 +571,13 @@
         <v>222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03616185018228242</v>
+        <v>0.01126637722081961</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05754870582821679</v>
+        <v>0.01735245457798264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1817694841828399</v>
+        <v>0.1519812695751963</v>
       </c>
     </row>
     <row r="7">
@@ -595,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08327313946556525</v>
+        <v>0.0007206265099467535</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08327313946556525</v>
+        <v>0.0007206265099467535</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>1596</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03564226807949819</v>
+        <v>0.0177767923997359</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04853669968634118</v>
+        <v>0.02585478571550861</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4324781171523208</v>
+        <v>0.2207634995441043</v>
       </c>
     </row>
     <row r="9">
@@ -643,13 +643,13 @@
         <v>114</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08549783722572291</v>
+        <v>0.01376880236945012</v>
       </c>
       <c r="E9" t="n">
-        <v>0.109665400434191</v>
+        <v>0.01851656134194819</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2850299182972178</v>
+        <v>0.1208530152529703</v>
       </c>
     </row>
     <row r="10">
@@ -667,13 +667,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.202339373904928</v>
+        <v>0.01141147200184423</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.202339373904928</v>
+        <v>0.01141147200184423</v>
       </c>
     </row>
   </sheetData>
